--- a/output/pdf_financials_xlsx/FFU.xlsx
+++ b/output/pdf_financials_xlsx/FFU.xlsx
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.259054</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.585145</v>
       </c>
     </row>
     <row r="93">
@@ -2694,7 +2694,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>1.259054</v>
       </c>

--- a/output/pdf_financials_xlsx/FFU.xlsx
+++ b/output/pdf_financials_xlsx/FFU.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.452285</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.452285</v>
       </c>
     </row>
     <row r="11">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000425</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.10923</v>
       </c>
     </row>
     <row r="102">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.003266</v>
+        <v>-0.003691</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.440001</v>
+        <v>0.330771</v>
       </c>
     </row>
     <row r="107">
@@ -3122,7 +3122,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.000425</v>
       </c>
@@ -3540,7 +3544,11 @@
           <t>Consulting &amp; directors’ fees 12</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
